--- a/projetPFA/outputs/test_Machines_Test_NonOrganise.xlsx
+++ b/projetPFA/outputs/test_Machines_Test_NonOrganise.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="Lignes_utiles" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Lignes_rejetees" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -542,7 +541,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.845</v>
       </c>
     </row>
     <row r="3">
@@ -603,7 +602,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="4">
@@ -664,7 +663,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="5">
@@ -725,7 +724,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.985</v>
+        <v>0.965</v>
       </c>
     </row>
     <row r="6">
@@ -786,33 +785,33 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.97</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BC48842</t>
+          <t>BC10392</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>K. Haddad</t>
+          <t>L. Perrin</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Assembly board to board_852054</t>
+          <t>SMC Adaptor_492349</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>TechnoFix SARL</t>
+          <t>IndustrIA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BTB</t>
+          <t>SMT</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -821,11 +820,11 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>9.92</v>
+        <v>4.52</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>En maintenance</t>
+          <t>Actif</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -839,15 +838,15 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>3608.4</v>
+        <v>3419.7</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>08/05/2025</t>
+          <t>06/01/2025</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.67</v>
+        <v>0.985</v>
       </c>
     </row>
     <row r="8">
@@ -863,26 +862,26 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SMC Adaptor_492349</t>
+          <t>E-Test Leshin_999147</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>IndustrIA</t>
+          <t>TechnoFix SARL</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SMT</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>urgent</t>
+          <t>RAS</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>4.52</v>
+        <v>7.82</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -891,40 +890,40 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Moyenne</t>
+          <t>Haute</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>3419.7</v>
+        <v>4197.9</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>06/01/2025</t>
+          <t>06/12/2025</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BC10392</t>
+          <t>BC78212</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>L. Perrin</t>
+          <t>K. Haddad</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>E-Test Leshin_999147</t>
+          <t>Optimel Ferite_897829</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -934,16 +933,16 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>BTB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>RAS</t>
+          <t>changement de pièce prévu</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>7.82</v>
+        <v>1.48</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -952,30 +951,30 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Haute</t>
+          <t>Moyenne</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>4197.9</v>
+        <v>4426.1</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>06/12/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.995</v>
+        <v>0.765</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BC78212</t>
+          <t>BC32062</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -985,7 +984,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Optimel Ferite_897829</t>
+          <t>Robot de soudure_491923</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -995,16 +994,16 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BTB</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>changement de pièce prévu</t>
+          <t>urgent</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1.48</v>
+        <v>12.16</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1013,30 +1012,30 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Moyenne</t>
+          <t>Basse</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>4426.1</v>
+        <v>2640.2</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>23/11/2025</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BC32062</t>
+          <t>BC74344</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1046,12 +1045,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Robot de soudure_491923</t>
+          <t>Robot de soudure_267651</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>TechnoFix SARL</t>
+          <t>AutoMach Europe</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1061,20 +1060,20 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>urgent</t>
+          <t>voir rapport maintenance</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>12.16</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Actif</t>
+          <t>En maintenance</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1083,41 +1082,41 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>2640.2</v>
+        <v>3755.7</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>23/11/2025</t>
+          <t>08/03/2025</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.96</v>
+        <v>0.945</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BC74344</t>
+          <t>BC10392</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>K. Haddad</t>
+          <t>A. Dupont</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Robot de soudure_267651</t>
+          <t>Camera inspection_737389</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AutoMach Europe</t>
+          <t>MécaPro</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>SMT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1126,7 +1125,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>8.210000000000001</v>
+        <v>5.98</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1144,11 +1143,11 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>3755.7</v>
+        <v>4078.8</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>08/03/2025</t>
+          <t>27/07/2025</t>
         </is>
       </c>
       <c r="M12" t="n">
@@ -1158,40 +1157,40 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BC10392</t>
+          <t>BC47072</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A. Dupont</t>
+          <t>K. Haddad</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Camera inspection_737389</t>
+          <t>Testeur fonctionnel_703845</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MécaPro</t>
+          <t>TechnoFix SARL</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SMT</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>voir rapport maintenance</t>
+          <t>à vérifier</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>5.98</v>
+        <v>0.05</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>En maintenance</t>
+          <t>Actif</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1201,35 +1200,35 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Basse</t>
+          <t>Moyenne</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>4078.8</v>
+        <v>4748.5</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>27/07/2025</t>
+          <t>02/12/2025</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0.855</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BC47072</t>
+          <t>BC14312</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>K. Haddad</t>
+          <t>L. Perrin</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Testeur fonctionnel_703845</t>
+          <t>Presse hydraulique_608530</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1239,16 +1238,16 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>SMT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>à vérifier</t>
+          <t>urgent</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.05</v>
+        <v>7.11</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1257,59 +1256,59 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Moyenne</t>
+          <t>Haute</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>4748.5</v>
+        <v>4458.8</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>02/12/2025</t>
+          <t>23/08/2025</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.975</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BC14312</t>
+          <t>BC87288</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>L. Perrin</t>
+          <t>K. Haddad</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Presse hydraulique_608530</t>
+          <t>Convoyeur_458121</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>TechnoFix SARL</t>
+          <t>AutoMach Europe</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SMT</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>urgent</t>
+          <t>à vérifier</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>7.11</v>
+        <v>14.2</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1318,59 +1317,59 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Haute</t>
+          <t>Moyenne</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>4458.8</v>
+        <v>3264.9</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>23/08/2025</t>
+          <t>08/11/2025</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BC87288</t>
+          <t>BC10392</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>K. Haddad</t>
+          <t>A. Dupont</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Convoyeur_458121</t>
+          <t>Testeur fonctionnel_845934</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AutoMach Europe</t>
+          <t>TechnoFix SARL</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>Packing</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>à vérifier</t>
+          <t>urgent</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>14.2</v>
+        <v>6.44</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1379,7 +1378,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1388,50 +1387,50 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>3264.9</v>
+        <v>4001.8</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>08/11/2025</t>
+          <t>15/02/2025</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0.885</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BC10392</t>
+          <t>BC51343</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>A. Dupont</t>
+          <t>J. Martin</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Testeur fonctionnel_845934</t>
+          <t>Camera inspection_279846</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>TechnoFix SARL</t>
+          <t>MécaPro</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Packing</t>
+          <t>BTB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>urgent</t>
+          <t>voir rapport maintenance</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>6.44</v>
+        <v>0.05</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1440,40 +1439,40 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Moyenne</t>
+          <t>Basse</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>4001.8</v>
+        <v>4834.9</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>15/02/2025</t>
+          <t>20/04/2025</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BC51343</t>
+          <t>BC44756</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>J. Martin</t>
+          <t>A. Dupont</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Camera inspection_279846</t>
+          <t>Camera inspection_863921</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1483,16 +1482,16 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>BTB</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>voir rapport maintenance</t>
+          <t>RAS</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.05</v>
+        <v>5.27</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1501,59 +1500,59 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Basse</t>
+          <t>Moyenne</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>4834.9</v>
+        <v>3723</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>20/04/2025</t>
+          <t>21/06/2025</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BC44756</t>
+          <t>BC13044</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>A. Dupont</t>
+          <t>S. Benali</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Camera inspection_863921</t>
+          <t>Camera inspection_874570</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MécaPro</t>
+          <t>TechnoFix SARL</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>SMT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>RAS</t>
+          <t>urgent</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>5.27</v>
+        <v>2.49</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1562,50 +1561,50 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Moyenne</t>
+          <t>Haute</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>3723</v>
+        <v>3257</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>21/06/2025</t>
+          <t>01/08/2025</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BC13044</t>
+          <t>BC39294</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>S. Benali</t>
+          <t>L. Perrin</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Camera inspection_874570</t>
+          <t>Camera inspection_767118</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>TechnoFix SARL</t>
+          <t>MécaPro</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SMT</t>
+          <t>BTB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1614,7 +1613,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>2.49</v>
+        <v>1.33</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1632,50 +1631,50 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>3257</v>
+        <v>4485.3</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>01/08/2025</t>
+          <t>15/04/2025</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.995</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BC39294</t>
+          <t>BC20855</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>L. Perrin</t>
+          <t>S. Benali</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Camera inspection_767118</t>
+          <t>E-Test Leshin_662274</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MécaPro</t>
+          <t>AutoMach Europe</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>BTB</t>
+          <t>SMT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>urgent</t>
+          <t>voir rapport maintenance</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1.33</v>
+        <v>11.56</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1684,7 +1683,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1693,50 +1692,50 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>4485.3</v>
+        <v>2717.7</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>15/04/2025</t>
+          <t>01/11/2025</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>0.995</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BC20855</t>
+          <t>BC29029</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>S. Benali</t>
+          <t>J. Martin</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>E-Test Leshin_662274</t>
+          <t>Testeur fonctionnel_886351</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>AutoMach Europe</t>
+          <t>TechnoFix SARL</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SMT</t>
+          <t>BTB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>voir rapport maintenance</t>
+          <t>RAS</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>11.56</v>
+        <v>3.26</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1745,30 +1744,30 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Haute</t>
+          <t>Moyenne</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>2717.7</v>
+        <v>5072.3</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>01/11/2025</t>
+          <t>23/08/2025</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BC29029</t>
+          <t>BC24104</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1778,7 +1777,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Testeur fonctionnel_886351</t>
+          <t>Station de vissage_833423</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1788,16 +1787,16 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>BTB</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>RAS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>3.26</v>
+        <v>11.54</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1806,7 +1805,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1815,31 +1814,31 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>5072.3</v>
+        <v>3998.9</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>23/08/2025</t>
+          <t>01/11/2025</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BC24104</t>
+          <t>BC29140</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>J. Martin</t>
+          <t>S. Benali</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Station de vissage_833423</t>
+          <t>SMC Adaptor_989163</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1854,11 +1853,11 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>urgent</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>11.54</v>
+        <v>5.82</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1867,7 +1866,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1876,31 +1875,31 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>3998.9</v>
+        <v>3874.7</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>01/11/2025</t>
+          <t>15/03/2025</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>0.975</v>
+        <v>0.925</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BC29140</t>
+          <t>BC74293</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>S. Benali</t>
+          <t>L. Perrin</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SMC Adaptor_989163</t>
+          <t>Assembly board to board_814279</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1919,7 +1918,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>5.82</v>
+        <v>6.99</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1928,7 +1927,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1937,41 +1936,41 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>3874.7</v>
+        <v>3858.55</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>15/03/2025</t>
+          <t>01/11/2025</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BC74293</t>
+          <t>BC10392</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>L. Perrin</t>
+          <t>S. Benali</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Assembly board to board_814279</t>
+          <t>SMC Adaptor_374704</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>TechnoFix SARL</t>
+          <t>AutoMach Europe</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1980,7 +1979,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>6.99</v>
+        <v>4.25</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1989,30 +1988,30 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Moyenne</t>
+          <t>Haute</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>3858.55</v>
+        <v>4437.7</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>01/11/2025</t>
+          <t>26/01/2025</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BC10392</t>
+          <t>BC61100</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2022,17 +2021,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SMC Adaptor_374704</t>
+          <t>Optimel Ferite_387378</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>AutoMach Europe</t>
+          <t>TechnoFix SARL</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>BTB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2041,11 +2040,11 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>4.25</v>
+        <v>4.73</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Actif</t>
+          <t>Hors service</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2055,35 +2054,35 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Haute</t>
+          <t>Moyenne</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>4437.7</v>
+        <v>5213.1</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>26/01/2025</t>
+          <t>01/11/2025</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>0.995</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BC61100</t>
+          <t>BC49057</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>S. Benali</t>
+          <t>K. Haddad</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Optimel Ferite_387378</t>
+          <t>SMC Adaptor_621515</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2093,7 +2092,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>BTB</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2102,16 +2101,16 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>4.73</v>
+        <v>5.78</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Hors service</t>
+          <t>Actif</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2120,21 +2119,21 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>5213.1</v>
+        <v>3192.3</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>01/11/2025</t>
+          <t>06/09/2025</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>0.97</v>
+        <v>0.905</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BC49057</t>
+          <t>BC10392</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2144,17 +2143,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SMC Adaptor_621515</t>
+          <t>Optimel Ferite_516243</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>TechnoFix SARL</t>
+          <t>IndustrIA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>BTB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2163,7 +2162,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>5.78</v>
+        <v>12.79</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2172,7 +2171,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2181,21 +2180,21 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>3192.3</v>
+        <v>4691.2</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>06/09/2025</t>
+          <t>08/10/2025</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>0.975</v>
+        <v>0.825</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BC10392</t>
+          <t>BC52944</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2205,12 +2204,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Optimel Ferite_516243</t>
+          <t>Convoyeur_250281</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IndustrIA</t>
+          <t>AutoMach Europe</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2220,58 +2219,58 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>urgent</t>
+          <t>à vérifier</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>12.79</v>
+        <v>13.85</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Actif</t>
+          <t>En maintenance</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Moyenne</t>
+          <t>Haute</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>4691.2</v>
+        <v>1891</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>08/10/2025</t>
+          <t>01/11/2025</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BC52944</t>
+          <t>BC39313</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>K. Haddad</t>
+          <t>L. Perrin</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Convoyeur_250281</t>
+          <t>SMC Adaptor_656091</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>AutoMach Europe</t>
+          <t>MécaPro</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2281,11 +2280,11 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>à vérifier</t>
+          <t>changement de pièce prévu</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>13.85</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2294,40 +2293,40 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Haute</t>
+          <t>Basse</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>1891</v>
+        <v>4157.6</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>01/11/2025</t>
+          <t>28/08/2025</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BC39313</t>
+          <t>BC10392</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>L. Perrin</t>
+          <t>S. Benali</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SMC Adaptor_656091</t>
+          <t>Optimel Ferite_882225</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2342,15 +2341,15 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>changement de pièce prévu</t>
+          <t>urgent</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>8.529999999999999</v>
+        <v>12.63</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>En maintenance</t>
+          <t>Actif</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2360,40 +2359,40 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Basse</t>
+          <t>Haute</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>4157.6</v>
+        <v>3701.3</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>28/08/2025</t>
+          <t>16/04/2025</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>0.995</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BC10392</t>
+          <t>BC95825</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>S. Benali</t>
+          <t>K. Haddad</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Optimel Ferite_882225</t>
+          <t>Testeur fonctionnel_486071</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>MécaPro</t>
+          <t>TechnoFix SARL</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2403,20 +2402,20 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>urgent</t>
+          <t>voir rapport maintenance</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>12.63</v>
+        <v>5.71</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Actif</t>
+          <t>En maintenance</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2425,31 +2424,31 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>3701.3</v>
+        <v>3858.55</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>16/04/2025</t>
+          <t>15/08/2025</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>0.98</v>
+        <v>0.945</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BC95825</t>
+          <t>BC54587</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>K. Haddad</t>
+          <t>S. Benali</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Testeur fonctionnel_486071</t>
+          <t>Camera inspection_827778</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2459,20 +2458,20 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>BTB</t>
+          <t>Packing</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>voir rapport maintenance</t>
+          <t>urgent</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>5.71</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>En maintenance</t>
+          <t>Hors service</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2482,40 +2481,40 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Haute</t>
+          <t>Moyenne</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>3858.55</v>
+        <v>4016.8</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>15/08/2025</t>
+          <t>06/08/2025</t>
         </is>
       </c>
       <c r="M34" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BC54587</t>
+          <t>BC86590</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>S. Benali</t>
+          <t>L. Perrin</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Camera inspection_827778</t>
+          <t>Testeur fonctionnel_716995</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>TechnoFix SARL</t>
+          <t>IndustrIA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2529,16 +2528,16 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>8.300000000000001</v>
+        <v>4.47</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Hors service</t>
+          <t>Actif</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2547,11 +2546,11 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>4016.8</v>
+        <v>5229.3</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>06/08/2025</t>
+          <t>26/03/2025</t>
         </is>
       </c>
       <c r="M35" t="n">
@@ -2561,36 +2560,36 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BC86590</t>
+          <t>BC10392</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>L. Perrin</t>
+          <t>K. Haddad</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Testeur fonctionnel_716995</t>
+          <t>E-Test Leshin_661851</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>IndustrIA</t>
+          <t>AutoMach Europe</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Packing</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>urgent</t>
+          <t>voir rapport maintenance</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>4.47</v>
+        <v>11.4</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2599,7 +2598,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2608,21 +2607,21 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>5229.3</v>
+        <v>2230.3</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>26/03/2025</t>
+          <t>18/10/2025</t>
         </is>
       </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>0.965</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BC10392</t>
+          <t>BC92915</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2632,35 +2631,35 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>E-Test Leshin_661851</t>
+          <t>Presse hydraulique_762514</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>AutoMach Europe</t>
+          <t>TechnoFix SARL</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Packing</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>voir rapport maintenance</t>
+          <t>à vérifier</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>11.4</v>
+        <v>5.62</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Actif</t>
+          <t>Hors service</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2669,31 +2668,31 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>2230.3</v>
+        <v>3946.8</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>18/10/2025</t>
+          <t>16/07/2025</t>
         </is>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
+        <v>0.905</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BC92915</t>
+          <t>BC10392</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>K. Haddad</t>
+          <t>S. Benali</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Presse hydraulique_762514</t>
+          <t>E-Test Leshin_495179</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2708,15 +2707,15 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>à vérifier</t>
+          <t>urgent</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>5.62</v>
+        <v>0.05</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Hors service</t>
+          <t>Actif</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2730,31 +2729,31 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>3946.8</v>
+        <v>3828.7</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>16/07/2025</t>
+          <t>01/06/2025</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>0.99</v>
+        <v>0.925</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BC10392</t>
+          <t>BC86122</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>S. Benali</t>
+          <t>K. Haddad</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>E-Test Leshin_495179</t>
+          <t>Camera inspection_608248</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2769,11 +2768,11 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>urgent</t>
+          <t>RAS</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2787,25 +2786,25 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Moyenne</t>
+          <t>Haute</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>3828.7</v>
+        <v>3858.55</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>01/06/2025</t>
+          <t>18/07/2025</t>
         </is>
       </c>
       <c r="M39" t="n">
-        <v>0.98</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BC86122</t>
+          <t>BC54181</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2815,26 +2814,26 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Camera inspection_608248</t>
+          <t>Robot de soudure_223916</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>TechnoFix SARL</t>
+          <t>AutoMach Europe</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Packing</t>
+          <t>BTB</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>RAS</t>
+          <t>urgent</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.98</v>
+        <v>12.38</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2848,7 +2847,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Haute</t>
+          <t>Basse</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2856,17 +2855,17 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>18/07/2025</t>
+          <t>26/12/2025</t>
         </is>
       </c>
       <c r="M40" t="n">
-        <v>0.99</v>
+        <v>0.8149999999999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BC54181</t>
+          <t>BC10392</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2876,12 +2875,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Robot de soudure_223916</t>
+          <t>Testeur fonctionnel_159943</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>AutoMach Europe</t>
+          <t>MécaPro</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2895,11 +2894,11 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>12.38</v>
+        <v>6.8</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Actif</t>
+          <t>Hors service</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2913,15 +2912,15 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>3858.55</v>
+        <v>5113.8</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>26/12/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="M41" t="n">
-        <v>0.945</v>
+        <v>0.885</v>
       </c>
     </row>
     <row r="42">
@@ -2932,31 +2931,31 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>K. Haddad</t>
+          <t>J. Martin</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Testeur fonctionnel_159943</t>
+          <t>Robot de soudure_583911</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>MécaPro</t>
+          <t>IndustrIA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>BTB</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>urgent</t>
+          <t>RAS</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>6.8</v>
+        <v>6.99</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -2965,40 +2964,40 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Basse</t>
+          <t>Haute</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>5113.8</v>
+        <v>2224.7</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>15/02/2025</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BC10392</t>
+          <t>BC43673</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>J. Martin</t>
+          <t>L. Perrin</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Robot de soudure_583911</t>
+          <t>SMC Adaptor_705079</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3008,12 +3007,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>SMT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>RAS</t>
+          <t>changement de pièce prévu</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -3021,7 +3020,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Hors service</t>
+          <t>Actif</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3031,35 +3030,35 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Haute</t>
+          <t>Moyenne</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>2224.7</v>
+        <v>3132.6</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>15/02/2025</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>0.985</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BC43673</t>
+          <t>BC29578</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>L. Perrin</t>
+          <t>A. Dupont</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SMC Adaptor_705079</t>
+          <t>Station de vissage_508224</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3069,16 +3068,16 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SMT</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>changement de pièce prévu</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>6.99</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -3087,7 +3086,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3096,21 +3095,21 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>3132.6</v>
+        <v>4322.9</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
+          <t>01/11/2025</t>
         </is>
       </c>
       <c r="M44" t="n">
-        <v>1</v>
+        <v>0.975</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BC29578</t>
+          <t>BC51819</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3120,26 +3119,26 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Station de vissage_508224</t>
+          <t>Camera inspection_817912</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>IndustrIA</t>
+          <t>AutoMach Europe</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>BTB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>RAS</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>9.119999999999999</v>
+        <v>15.19</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -3148,30 +3147,30 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Moyenne</t>
+          <t>Haute</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>4322.9</v>
+        <v>3129.8</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>01/11/2025</t>
+          <t>01/05/2025</t>
         </is>
       </c>
       <c r="M45" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BC51819</t>
+          <t>BC10392</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3181,12 +3180,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Camera inspection_817912</t>
+          <t>E-Test Leshin_133268</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>AutoMach Europe</t>
+          <t>TechnoFix SARL</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3196,11 +3195,11 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>RAS</t>
+          <t>urgent</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>15.19</v>
+        <v>12.36</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -3209,7 +3208,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3218,31 +3217,31 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>3129.8</v>
+        <v>3858.55</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>01/05/2025</t>
+          <t>01/11/2025</t>
         </is>
       </c>
       <c r="M46" t="n">
-        <v>1</v>
+        <v>0.925</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BC10392</t>
+          <t>BC67761</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>A. Dupont</t>
+          <t>J. Martin</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>E-Test Leshin_133268</t>
+          <t>Assembly board to board_943448</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3257,11 +3256,11 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>urgent</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>12.36</v>
+        <v>6.99</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -3275,35 +3274,35 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Haute</t>
+          <t>Moyenne</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>3858.55</v>
+        <v>3842.4</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>01/11/2025</t>
+          <t>20/07/2025</t>
         </is>
       </c>
       <c r="M47" t="n">
-        <v>0.97</v>
+        <v>0.825</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BC67761</t>
+          <t>BC50188</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>J. Martin</t>
+          <t>S. Benali</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Assembly board to board_943448</t>
+          <t>Assembly board to board_738479</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3313,25 +3312,25 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>BTB</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>urgent</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>6.99</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Actif</t>
+          <t>En maintenance</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3340,41 +3339,41 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>3842.4</v>
+        <v>3906.7</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>20/07/2025</t>
+          <t>01/11/2025</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>0.89</v>
+        <v>0.905</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BC50188</t>
+          <t>BC10392</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>S. Benali</t>
+          <t>L. Perrin</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Assembly board to board_738479</t>
+          <t>Testeur fonctionnel_705765</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>TechnoFix SARL</t>
+          <t>MécaPro</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>BTB</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3383,16 +3382,16 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>9.029999999999999</v>
+        <v>7.15</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>En maintenance</t>
+          <t>Actif</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3401,11 +3400,11 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>3906.7</v>
+        <v>5098.7</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>01/11/2025</t>
+          <t>15/09/2025</t>
         </is>
       </c>
       <c r="M49" t="n">
@@ -3415,22 +3414,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BC10392</t>
+          <t>BC80430</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>L. Perrin</t>
+          <t>K. Haddad</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Testeur fonctionnel_705765</t>
+          <t>Station de vissage_295513</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>MécaPro</t>
+          <t>TechnoFix SARL</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3440,20 +3439,20 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>urgent</t>
+          <t>RAS</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>7.15</v>
+        <v>5.36</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Actif</t>
+          <t>Hors service</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3462,36 +3461,36 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>5098.7</v>
+        <v>3785.2</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>15/09/2025</t>
+          <t>02/02/2025</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>0.995</v>
+        <v>0.715</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BC80430</t>
+          <t>BC74724</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>K. Haddad</t>
+          <t>L. Perrin</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Station de vissage_295513</t>
+          <t>Optimel Ferite_440363</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>TechnoFix SARL</t>
+          <t>MécaPro</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3501,20 +3500,20 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>RAS</t>
+          <t>urgent</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>5.36</v>
+        <v>10.54</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Hors service</t>
+          <t>Actif</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3523,36 +3522,36 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>3785.2</v>
+        <v>3012.9</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>02/02/2025</t>
+          <t>09/11/2025</t>
         </is>
       </c>
       <c r="M51" t="n">
-        <v>0.91</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BC74724</t>
+          <t>BC36976</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>L. Perrin</t>
+          <t>J. Martin</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Optimel Ferite_440363</t>
+          <t>Convoyeur_887879</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>MécaPro</t>
+          <t>IndustrIA</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3566,7 +3565,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>10.54</v>
+        <v>6.23</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -3575,7 +3574,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3584,21 +3583,21 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>3012.9</v>
+        <v>3366.6</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>09/11/2025</t>
+          <t>10/12/2025</t>
         </is>
       </c>
       <c r="M52" t="n">
-        <v>0.98</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BC36976</t>
+          <t>BC85102</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3608,12 +3607,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Convoyeur_887879</t>
+          <t>Assembly board to board_428851</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>IndustrIA</t>
+          <t>TechnoFix SARL</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3623,11 +3622,11 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>urgent</t>
+          <t>changement de pièce prévu</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>6.23</v>
+        <v>6.83</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -3641,35 +3640,35 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Moyenne</t>
+          <t>Haute</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>3366.6</v>
+        <v>5139</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>10/12/2025</t>
+          <t>01/11/2025</t>
         </is>
       </c>
       <c r="M53" t="n">
-        <v>0.975</v>
+        <v>0.985</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BC85102</t>
+          <t>BC10392</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>J. Martin</t>
+          <t>K. Haddad</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Assembly board to board_428851</t>
+          <t>Station de vissage_296685</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3679,16 +3678,16 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>BTB</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>changement de pièce prévu</t>
+          <t>RAS</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>6.83</v>
+        <v>18.29</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -3697,24 +3696,24 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Haute</t>
+          <t>Moyenne</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>5139</v>
+        <v>3272.8</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>01/11/2025</t>
+          <t>27/12/2025</t>
         </is>
       </c>
       <c r="M54" t="n">
-        <v>0.985</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="55">
@@ -3725,12 +3724,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>K. Haddad</t>
+          <t>L. Perrin</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Station de vissage_296685</t>
+          <t>Convoyeur_944399</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3740,42 +3739,42 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>SMT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>RAS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>18.29</v>
+        <v>7.01</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Actif</t>
+          <t>Hors service</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Moyenne</t>
+          <t>Basse</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>3272.8</v>
+        <v>3575.5</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>27/12/2025</t>
+          <t>05/03/2025</t>
         </is>
       </c>
       <c r="M55" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="56">
@@ -3786,73 +3785,73 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>L. Perrin</t>
+          <t>S. Benali</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Convoyeur_944399</t>
+          <t>Convoyeur_261894</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>TechnoFix SARL</t>
+          <t>MécaPro</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>SMT</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>urgent</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>7.01</v>
+        <v>5</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Hors service</t>
+          <t>En maintenance</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Basse</t>
+          <t>Moyenne</t>
         </is>
       </c>
       <c r="K56" t="n">
-        <v>3575.5</v>
+        <v>3267.4</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>05/03/2025</t>
+          <t>06/09/2025</t>
         </is>
       </c>
       <c r="M56" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BC10392</t>
+          <t>BC47119</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>S. Benali</t>
+          <t>K. Haddad</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Convoyeur_261894</t>
+          <t>SMC Adaptor_845884</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3862,25 +3861,25 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>SMT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>urgent</t>
+          <t>changement de pièce prévu</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>5</v>
+        <v>17.42</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>En maintenance</t>
+          <t>Actif</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3889,54 +3888,54 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>3267.4</v>
+        <v>3274.6</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>06/09/2025</t>
+          <t>09/06/2025</t>
         </is>
       </c>
       <c r="M57" t="n">
-        <v>1</v>
+        <v>0.965</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BC47119</t>
+          <t>BC34862</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>K. Haddad</t>
+          <t>A. Dupont</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SMC Adaptor_845884</t>
+          <t>Convoyeur_376445</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>MécaPro</t>
+          <t>IndustrIA</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>SMT</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>changement de pièce prévu</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>17.42</v>
+        <v>7.5</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Actif</t>
+          <t>Hors service</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3946,35 +3945,35 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Moyenne</t>
+          <t>Basse</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>3274.6</v>
+        <v>3959.4</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>09/06/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>0.995</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BC34862</t>
+          <t>BC42574</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>A. Dupont</t>
+          <t>K. Haddad</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Convoyeur_376445</t>
+          <t>E-Test Leshin_667065</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3984,77 +3983,77 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>BTB</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>urgent</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>7.5</v>
+        <v>13.14</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Hors service</t>
+          <t>Actif</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Basse</t>
+          <t>Haute</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>3959.4</v>
+        <v>3687.6</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="M59" t="n">
-        <v>1</v>
+        <v>0.905</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BC42574</t>
+          <t>BC24591</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>K. Haddad</t>
+          <t>S. Benali</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>E-Test Leshin_667065</t>
+          <t>SMC Adaptor_243532</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>IndustrIA</t>
+          <t>TechnoFix SARL</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>BTB</t>
+          <t>Packing</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>urgent</t>
+          <t>à vérifier</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>13.14</v>
+        <v>6.99</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -4068,35 +4067,35 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Haute</t>
+          <t>Moyenne</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>3687.6</v>
+        <v>4188.9</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>15/12/2025</t>
         </is>
       </c>
       <c r="M60" t="n">
-        <v>0.965</v>
+        <v>0.855</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BC24591</t>
+          <t>BC35912</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>S. Benali</t>
+          <t>K. Haddad</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SMC Adaptor_243532</t>
+          <t>Presse hydraulique_339500</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4106,7 +4105,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Packing</t>
+          <t>BTB</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4115,7 +4114,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>6.99</v>
+        <v>5.78</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -4129,35 +4128,35 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Moyenne</t>
+          <t>Basse</t>
         </is>
       </c>
       <c r="K61" t="n">
-        <v>4188.9</v>
+        <v>3731.3</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>15/12/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>0.925</v>
+        <v>0.825</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BC35912</t>
+          <t>BC10392</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>K. Haddad</t>
+          <t>A. Dupont</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Presse hydraulique_339500</t>
+          <t>E-Test Leshin_236612</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4167,16 +4166,16 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>BTB</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>à vérifier</t>
+          <t>voir rapport maintenance</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>5.78</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -4185,24 +4184,24 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Basse</t>
+          <t>Haute</t>
         </is>
       </c>
       <c r="K62" t="n">
-        <v>3731.3</v>
+        <v>4102.4</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>09/04/2025</t>
         </is>
       </c>
       <c r="M62" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4213,31 +4212,31 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>A. Dupont</t>
+          <t>L. Perrin</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>E-Test Leshin_236612</t>
+          <t>Assembly board to board_165603</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>TechnoFix SARL</t>
+          <t>AutoMach Europe</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>voir rapport maintenance</t>
+          <t>urgent</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>8.869999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -4246,59 +4245,59 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Haute</t>
+          <t>Moyenne</t>
         </is>
       </c>
       <c r="K63" t="n">
-        <v>4102.4</v>
+        <v>2551.5</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>09/04/2025</t>
+          <t>23/03/2025</t>
         </is>
       </c>
       <c r="M63" t="n">
-        <v>0.995</v>
+        <v>0.985</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BC10392</t>
+          <t>BC77353</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>L. Perrin</t>
+          <t>S. Benali</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Assembly board to board_165603</t>
+          <t>Presse hydraulique_932786</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>AutoMach Europe</t>
+          <t>MécaPro</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>BTB</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>urgent</t>
+          <t>voir rapport maintenance</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0.79</v>
+        <v>7.76</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -4316,50 +4315,50 @@
         </is>
       </c>
       <c r="K64" t="n">
-        <v>2551.5</v>
+        <v>3937.5</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>23/03/2025</t>
+          <t>10/03/2025</t>
         </is>
       </c>
       <c r="M64" t="n">
-        <v>0.99</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BC77353</t>
+          <t>BC58545</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>S. Benali</t>
+          <t>K. Haddad</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Presse hydraulique_932786</t>
+          <t>Assembly board to board_237419</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>MécaPro</t>
+          <t>IndustrIA</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>BTB</t>
+          <t>SMT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>voir rapport maintenance</t>
+          <t>urgent</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>7.76</v>
+        <v>3.68</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -4377,21 +4376,21 @@
         </is>
       </c>
       <c r="K65" t="n">
-        <v>3937.5</v>
+        <v>2853.4</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>10/03/2025</t>
+          <t>01/11/2025</t>
         </is>
       </c>
       <c r="M65" t="n">
-        <v>0.965</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BC58545</t>
+          <t>BC30107</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4401,17 +4400,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Assembly board to board_237419</t>
+          <t>Presse hydraulique_811637</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>IndustrIA</t>
+          <t>TechnoFix SARL</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>SMT</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4420,16 +4419,16 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>3.68</v>
+        <v>6.99</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Actif</t>
+          <t>En maintenance</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4438,41 +4437,41 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>2853.4</v>
+        <v>3858.55</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>01/11/2025</t>
+          <t>23/05/2025</t>
         </is>
       </c>
       <c r="M66" t="n">
-        <v>0.985</v>
+        <v>0.865</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BC30107</t>
+          <t>BC10392</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>K. Haddad</t>
+          <t>L. Perrin</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Presse hydraulique_811637</t>
+          <t>Optimel Ferite_747922</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>TechnoFix SARL</t>
+          <t>AutoMach Europe</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>SMT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4481,68 +4480,68 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>6.99</v>
+        <v>16.95</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>En maintenance</t>
+          <t>Actif</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Moyenne</t>
+          <t>Basse</t>
         </is>
       </c>
       <c r="K67" t="n">
-        <v>3858.55</v>
+        <v>3803.6</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>23/05/2025</t>
+          <t>18/08/2025</t>
         </is>
       </c>
       <c r="M67" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BC10392</t>
+          <t>BC30164</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>L. Perrin</t>
+          <t>A. Dupont</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Optimel Ferite_747922</t>
+          <t>Station de vissage_246369</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>AutoMach Europe</t>
+          <t>TechnoFix SARL</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>SMT</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>urgent</t>
+          <t>à vérifier</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>16.95</v>
+        <v>6.44</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -4551,59 +4550,59 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Basse</t>
+          <t>Moyenne</t>
         </is>
       </c>
       <c r="K68" t="n">
-        <v>3803.6</v>
+        <v>3858.55</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>18/08/2025</t>
+          <t>28/08/2025</t>
         </is>
       </c>
       <c r="M68" t="n">
-        <v>1</v>
+        <v>0.975</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BC30164</t>
+          <t>BC10416</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>A. Dupont</t>
+          <t>J. Martin</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Station de vissage_246369</t>
+          <t>E-Test Leshin_538298</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>TechnoFix SARL</t>
+          <t>IndustrIA</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>à vérifier</t>
+          <t>RAS</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>6.44</v>
+        <v>5.19</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -4612,30 +4611,30 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Moyenne</t>
+          <t>Basse</t>
         </is>
       </c>
       <c r="K69" t="n">
-        <v>3858.55</v>
+        <v>2523.7</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>28/08/2025</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="M69" t="n">
-        <v>0.995</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BC10416</t>
+          <t>BC38205</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4645,7 +4644,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>E-Test Leshin_538298</t>
+          <t>Camera inspection_589648</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4655,25 +4654,25 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>SMT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>RAS</t>
+          <t>voir rapport maintenance</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>5.19</v>
+        <v>6.08</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Actif</t>
+          <t>Hors service</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4682,228 +4681,15 @@
         </is>
       </c>
       <c r="K70" t="n">
-        <v>2523.7</v>
+        <v>4553.6</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>01/11/2025</t>
         </is>
       </c>
       <c r="M70" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>BC38205</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>J. Martin</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Camera inspection_589648</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>IndustrIA</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>SMT</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>voir rapport maintenance</t>
-        </is>
-      </c>
-      <c r="G71" t="n">
-        <v>6.08</v>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Hors service</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>Basse</t>
-        </is>
-      </c>
-      <c r="K71" t="n">
-        <v>4553.6</v>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>01/11/2025</t>
-        </is>
-      </c>
-      <c r="M71" t="n">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Code_Barre</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Responsable</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Nom de la machine</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Fournisseur</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Zone</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Commentaire_libre</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Taux_Defaut_pct</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Statut</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Catégorie</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Priorite_intervention</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Heures_Fonctionnement</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Date_derniere_MAJ</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>utilite_predite</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>score_confiance</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>BC10392</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>K. Haddad</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Convoyeur_000001</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>TechnoFix SARL</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>BTB</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>urgent</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Actif</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Moyenne</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>3858.55</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>01/11/2025</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>0.605</v>
       </c>
     </row>
   </sheetData>
